--- a/Digital Chess Clock/Grading/2 stage/3-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-04_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/3-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-04_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Digital Chess Clock/Grading/2 stage/2026-03-04/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Digital Chess Clock/Grading/2 stage/3-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815E6246-A855-2A49-A25B-6A387FF1E25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A0F563-A49F-A846-8489-7D271805E6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chess Clock" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -886,11 +886,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1058,20 +1067,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1096,8 +1108,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="6"/>
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1120,8 +1132,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1273,14 +1285,14 @@
       <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
     <tableStyle name="Metrics-style 2" pivot="0" count="3" xr9:uid="{6E4B6190-FE31-8A45-AD5D-128E318AA704}">
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
+      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+    </tableStyle>
+    <tableStyle name="Weighted Cohens Kappa-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
       <tableStyleElement type="headerRow" dxfId="2"/>
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="secondRowStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="Weighted Cohens Kappa-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1364,7 +1376,9 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Element"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Human"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="LLM"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="LLM">
+      <calculatedColumnFormula>'Chess Clock LLM-Based Grading'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Weighted Cohens Kappa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17520,17 +17534,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="69" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="J1" s="71" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="J1" s="65" t="s">
         <v>105</v>
       </c>
     </row>
@@ -17559,7 +17573,7 @@
       <c r="H2" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="J2" s="66" t="s">
         <v>157</v>
       </c>
     </row>
@@ -17629,7 +17643,7 @@
         <f t="shared" si="2"/>
         <v>0.91666666666666663</v>
       </c>
-      <c r="J4" s="71" t="s">
+      <c r="J4" s="65" t="s">
         <v>155</v>
       </c>
     </row>
@@ -17665,7 +17679,7 @@
         <f t="shared" si="2"/>
         <v>0.88888888888888895</v>
       </c>
-      <c r="J5" s="72" t="s">
+      <c r="J5" s="66" t="s">
         <v>156</v>
       </c>
     </row>
@@ -17836,16 +17850,16 @@
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="28" t="s">
@@ -19171,11 +19185,11 @@
       <c r="G1" s="68"/>
       <c r="H1" s="68"/>
       <c r="I1" s="68"/>
-      <c r="L1" s="69" t="s">
+      <c r="L1" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="str">
@@ -19451,11 +19465,11 @@
       <c r="G8" s="68"/>
       <c r="H8" s="68"/>
       <c r="I8" s="68"/>
-      <c r="L8" s="69" t="s">
+      <c r="L8" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -19728,11 +19742,11 @@
       <c r="G15" s="68"/>
       <c r="H15" s="68"/>
       <c r="I15" s="68"/>
-      <c r="L15" s="69" t="s">
+      <c r="L15" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -20005,11 +20019,11 @@
       <c r="G22" s="68"/>
       <c r="H22" s="68"/>
       <c r="I22" s="68"/>
-      <c r="L22" s="69" t="s">
+      <c r="L22" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -20282,11 +20296,11 @@
       <c r="G29" s="68"/>
       <c r="H29" s="68"/>
       <c r="I29" s="68"/>
-      <c r="L29" s="69" t="s">
+      <c r="L29" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="72"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -20559,11 +20573,11 @@
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
       <c r="I36" s="68"/>
-      <c r="L36" s="69" t="s">
+      <c r="L36" s="71" t="s">
         <v>140</v>
       </c>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="72"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -20836,11 +20850,11 @@
       <c r="G43" s="68"/>
       <c r="H43" s="68"/>
       <c r="I43" s="68"/>
-      <c r="L43" s="69" t="s">
+      <c r="L43" s="71" t="s">
         <v>142</v>
       </c>
-      <c r="M43" s="70"/>
-      <c r="N43" s="70"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="72"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -21113,11 +21127,11 @@
       <c r="G50" s="68"/>
       <c r="H50" s="68"/>
       <c r="I50" s="68"/>
-      <c r="L50" s="69" t="s">
+      <c r="L50" s="71" t="s">
         <v>144</v>
       </c>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
+      <c r="M50" s="72"/>
+      <c r="N50" s="72"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -22460,7 +22474,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4">
-        <f>'Chess Clock Human-Based Grading'!C2</f>
+        <f>'Chess Clock LLM-Based Grading'!C2</f>
         <v>1</v>
       </c>
       <c r="E2" s="27"/>
@@ -22530,7 +22544,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <f>'Chess Clock Human-Based Grading'!C3</f>
+        <f>'Chess Clock LLM-Based Grading'!C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="27"/>
@@ -22575,15 +22589,15 @@
       </c>
       <c r="R3" s="40">
         <f t="shared" ref="R3:T3" si="2">($J3/$J$6) * (G$6/$J$6)</f>
-        <v>2.0710059171597635E-2</v>
+        <v>5.9541420118343187E-2</v>
       </c>
       <c r="S3" s="41">
         <f t="shared" si="2"/>
-        <v>1.8121301775147928E-2</v>
+        <v>1.5532544378698224E-2</v>
       </c>
       <c r="T3" s="42">
         <f t="shared" si="2"/>
-        <v>9.5784023668639057E-2</v>
+        <v>5.9541420118343187E-2</v>
       </c>
       <c r="U3" s="11"/>
       <c r="V3" s="43" t="s">
@@ -22591,7 +22605,7 @@
       </c>
       <c r="W3" s="40">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>1.9230769230769232E-2</v>
+        <v>0.33653846153846156</v>
       </c>
       <c r="X3" s="42" t="s">
         <v>147</v>
@@ -22611,7 +22625,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <f>'Chess Clock Human-Based Grading'!C4</f>
+        <f>'Chess Clock LLM-Based Grading'!C4</f>
         <v>1</v>
       </c>
       <c r="E4" s="27"/>
@@ -22620,15 +22634,15 @@
       </c>
       <c r="G4" s="44">
         <f t="shared" ref="G4:I4" si="3">COUNTIFS($C$2:$C$46, $F4, $D$2:$D$46, G$2)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="11">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I4" s="45">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="11">
         <f t="shared" si="0"/>
@@ -22656,15 +22670,15 @@
       </c>
       <c r="R4" s="44">
         <f t="shared" ref="R4:T4" si="5">($J4/$J$6) * (G$6/$J$6)</f>
-        <v>2.0710059171597635E-2</v>
+        <v>5.9541420118343187E-2</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" si="5"/>
-        <v>1.8121301775147928E-2</v>
+        <v>1.5532544378698224E-2</v>
       </c>
       <c r="T4" s="45">
         <f t="shared" si="5"/>
-        <v>9.5784023668639057E-2</v>
+        <v>5.9541420118343187E-2</v>
       </c>
       <c r="U4" s="11"/>
       <c r="V4" s="43" t="s">
@@ -22672,7 +22686,7 @@
       </c>
       <c r="W4" s="44">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
-        <v>0.32470414201183434</v>
+        <v>0.49223372781065089</v>
       </c>
       <c r="X4" s="45" t="s">
         <v>149</v>
@@ -22692,7 +22706,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <f>'Chess Clock Human-Based Grading'!C5</f>
+        <f>'Chess Clock LLM-Based Grading'!C5</f>
         <v>1</v>
       </c>
       <c r="E5" s="27"/>
@@ -22701,15 +22715,15 @@
       </c>
       <c r="G5" s="46">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, G$2)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)+MAX(C53-D53,0)</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H5" s="47">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, H$2)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" s="48">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, I$2)+ SUM(MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52), MIN(C53,D53))</f>
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J5" s="11">
         <f t="shared" si="0"/>
@@ -22737,15 +22751,15 @@
       </c>
       <c r="R5" s="46">
         <f t="shared" ref="R5:T5" si="7">($J5/$J$6) * (G$6/$J$6)</f>
-        <v>0.11242603550295859</v>
+        <v>0.32322485207100587</v>
       </c>
       <c r="S5" s="47">
         <f t="shared" si="7"/>
-        <v>9.8372781065088746E-2</v>
+        <v>8.4319526627218935E-2</v>
       </c>
       <c r="T5" s="48">
         <f t="shared" si="7"/>
-        <v>0.5199704142011834</v>
+        <v>0.32322485207100587</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="43" t="s">
@@ -22753,7 +22767,7 @@
       </c>
       <c r="W5" s="46">
         <f>1-W3/W4</f>
-        <v>0.94077448747152626</v>
+        <v>0.31630353117956422</v>
       </c>
       <c r="X5" s="48" t="s">
         <v>150</v>
@@ -22773,7 +22787,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <f>'Chess Clock Human-Based Grading'!C6</f>
+        <f>'Chess Clock LLM-Based Grading'!C6</f>
         <v>1</v>
       </c>
       <c r="E6" s="27"/>
@@ -22782,15 +22796,15 @@
       </c>
       <c r="G6" s="11">
         <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="8"/>
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(G3:I5)</f>
@@ -22822,7 +22836,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <f>'Chess Clock Human-Based Grading'!C7</f>
+        <f>'Chess Clock LLM-Based Grading'!C7</f>
         <v>1</v>
       </c>
       <c r="E7" s="27"/>
@@ -22844,8 +22858,8 @@
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f>'Chess Clock Human-Based Grading'!C8</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C8</f>
+        <v>0.5</v>
       </c>
       <c r="E8" s="27"/>
       <c r="F8" s="67" t="s">
@@ -22869,8 +22883,8 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f>'Chess Clock Human-Based Grading'!C9</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C9</f>
+        <v>0</v>
       </c>
       <c r="E9" s="27"/>
       <c r="F9" s="11" t="s">
@@ -22939,8 +22953,8 @@
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <f>'Chess Clock Human-Based Grading'!C10</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C10</f>
+        <v>0.5</v>
       </c>
       <c r="E10" s="27"/>
       <c r="F10" s="39">
@@ -22984,11 +22998,11 @@
       </c>
       <c r="R10" s="40">
         <f t="shared" ref="R10:T10" si="12">($J10/$J$13) * (G$13/$J$13)</f>
-        <v>5.1020408163265302E-3</v>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="S10" s="41">
         <f t="shared" si="12"/>
-        <v>2.0408163265306121E-2</v>
+        <v>5.1020408163265302E-3</v>
       </c>
       <c r="T10" s="42">
         <f t="shared" si="12"/>
@@ -23000,7 +23014,7 @@
       </c>
       <c r="W10" s="40">
         <f>SUMPRODUCT(G10:I12, M10:O12) /$J$13</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="X10" s="42" t="s">
         <v>147</v>
@@ -23020,7 +23034,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <f>'Chess Clock Human-Based Grading'!C11</f>
+        <f>'Chess Clock LLM-Based Grading'!C11</f>
         <v>1</v>
       </c>
       <c r="E11" s="27"/>
@@ -23029,15 +23043,15 @@
       </c>
       <c r="G11" s="44">
         <f t="shared" ref="G11:I11" si="13">COUNTIFS($A$2:$A$90,$F$9,$C$2:$C$90,$F11,$D$2:$D$90,G$9)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" s="45">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="11">
         <f t="shared" si="10"/>
@@ -23065,11 +23079,11 @@
       </c>
       <c r="R11" s="44">
         <f t="shared" ref="R11:T11" si="15">($J11/$J$13) * (G$13/$J$13)</f>
-        <v>2.0408163265306121E-2</v>
+        <v>8.1632653061224483E-2</v>
       </c>
       <c r="S11" s="11">
         <f t="shared" si="15"/>
-        <v>8.1632653061224483E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="T11" s="45">
         <f t="shared" si="15"/>
@@ -23081,7 +23095,7 @@
       </c>
       <c r="W11" s="44">
         <f>SUMPRODUCT(R10:T12, M10:O12)</f>
-        <v>0.29591836734693877</v>
+        <v>0.38775510204081631</v>
       </c>
       <c r="X11" s="45" t="s">
         <v>149</v>
@@ -23101,8 +23115,8 @@
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <f>'Chess Clock Human-Based Grading'!C12</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C12</f>
+        <v>0</v>
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="39">
@@ -23110,15 +23124,15 @@
       </c>
       <c r="G12" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$9,$C$2:$C$46,$F12,$D$2:$D$46,G$9)+MAX(C47-D47,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="47">
         <f>COUNTIFS($A$2:$A$90,$F$9,$C$2:$C$90,$F12,$D$2:$D$90,H$9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="48">
         <f>COUNTIFS($A$2:$A$46,$F$9,$C$2:$C$46,$F12,$D$2:$D$46,I$9)+MIN(C47-D47)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J12" s="11">
         <f t="shared" si="10"/>
@@ -23146,11 +23160,11 @@
       </c>
       <c r="R12" s="46">
         <f t="shared" ref="R12:T12" si="17">($J12/$J$13) * (G$13/$J$13)</f>
-        <v>4.5918367346938778E-2</v>
+        <v>0.18367346938775511</v>
       </c>
       <c r="S12" s="47">
         <f t="shared" si="17"/>
-        <v>0.18367346938775511</v>
+        <v>4.5918367346938778E-2</v>
       </c>
       <c r="T12" s="48">
         <f t="shared" si="17"/>
@@ -23162,7 +23176,7 @@
       </c>
       <c r="W12" s="46">
         <f>1-W10/W11</f>
-        <v>1</v>
+        <v>0.35526315789473684</v>
       </c>
       <c r="X12" s="48" t="s">
         <v>150</v>
@@ -23182,8 +23196,8 @@
         <v>1</v>
       </c>
       <c r="D13" s="4">
-        <f>'Chess Clock Human-Based Grading'!C13</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C13</f>
+        <v>0</v>
       </c>
       <c r="E13" s="27"/>
       <c r="F13" s="49" t="s">
@@ -23191,11 +23205,11 @@
       </c>
       <c r="G13" s="11">
         <f t="shared" ref="G13:I13" si="18">SUM(G10:G12)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="18"/>
@@ -23220,7 +23234,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="4">
-        <f>'Chess Clock Human-Based Grading'!C14</f>
+        <f>'Chess Clock LLM-Based Grading'!C14</f>
         <v>1</v>
       </c>
       <c r="E14" s="27"/>
@@ -23239,7 +23253,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="4">
-        <f>'Chess Clock Human-Based Grading'!C15</f>
+        <f>'Chess Clock LLM-Based Grading'!C15</f>
         <v>1</v>
       </c>
       <c r="E15" s="27"/>
@@ -23264,8 +23278,8 @@
         <v>0.5</v>
       </c>
       <c r="D16" s="4">
-        <f>'Chess Clock Human-Based Grading'!C16</f>
-        <v>0.5</v>
+        <f>'Chess Clock LLM-Based Grading'!C16</f>
+        <v>0</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="11" t="s">
@@ -23334,8 +23348,8 @@
         <v>1</v>
       </c>
       <c r="D17" s="4">
-        <f>'Chess Clock Human-Based Grading'!C17</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C17</f>
+        <v>0</v>
       </c>
       <c r="E17" s="27"/>
       <c r="F17" s="39">
@@ -23379,7 +23393,7 @@
       </c>
       <c r="R17" s="40">
         <f t="shared" ref="R17:T17" si="22">($J17/$J$20) * (G$20/$J$20)</f>
-        <v>8.8888888888888889E-3</v>
+        <v>1.7777777777777778E-2</v>
       </c>
       <c r="S17" s="41">
         <f t="shared" si="22"/>
@@ -23387,7 +23401,7 @@
       </c>
       <c r="T17" s="42">
         <f t="shared" si="22"/>
-        <v>4.8888888888888885E-2</v>
+        <v>0.04</v>
       </c>
       <c r="U17" s="11"/>
       <c r="V17" s="43" t="s">
@@ -23395,7 +23409,7 @@
       </c>
       <c r="W17" s="40">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.2</v>
       </c>
       <c r="X17" s="42" t="s">
         <v>147</v>
@@ -23415,8 +23429,8 @@
         <v>0.5</v>
       </c>
       <c r="D18" s="4">
-        <f>'Chess Clock Human-Based Grading'!C18</f>
-        <v>0.5</v>
+        <f>'Chess Clock LLM-Based Grading'!C18</f>
+        <v>0</v>
       </c>
       <c r="E18" s="27"/>
       <c r="F18" s="39">
@@ -23460,7 +23474,7 @@
       </c>
       <c r="R18" s="44">
         <f t="shared" ref="R18:T18" si="25">($J18/$J$20) * (G$20/$J$20)</f>
-        <v>1.7777777777777778E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="S18" s="11">
         <f t="shared" si="25"/>
@@ -23468,7 +23482,7 @@
       </c>
       <c r="T18" s="45">
         <f t="shared" si="25"/>
-        <v>9.7777777777777769E-2</v>
+        <v>0.08</v>
       </c>
       <c r="U18" s="11"/>
       <c r="V18" s="43" t="s">
@@ -23476,7 +23490,7 @@
       </c>
       <c r="W18" s="44">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
-        <v>0.27111111111111114</v>
+        <v>0.36888888888888893</v>
       </c>
       <c r="X18" s="45" t="s">
         <v>149</v>
@@ -23496,8 +23510,8 @@
         <v>0.5</v>
       </c>
       <c r="D19" s="4">
-        <f>'Chess Clock Human-Based Grading'!C19</f>
-        <v>0.5</v>
+        <f>'Chess Clock LLM-Based Grading'!C19</f>
+        <v>0</v>
       </c>
       <c r="E19" s="27"/>
       <c r="F19" s="39">
@@ -23505,7 +23519,7 @@
       </c>
       <c r="G19" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,G$16)+MAX(C48-D48,0)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="47">
         <f>COUNTIFS($A$2:$A$90,$F$16,$C$2:$C$90,$F19,$D$2:$D$90,H$16)</f>
@@ -23513,7 +23527,7 @@
       </c>
       <c r="I19" s="48">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,I$16) + MIN(C48,D48)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J19" s="11">
         <f t="shared" si="20"/>
@@ -23541,7 +23555,7 @@
       </c>
       <c r="R19" s="46">
         <f t="shared" ref="R19:T19" si="27">($J19/$J$20) * (G$20/$J$20)</f>
-        <v>0.10666666666666667</v>
+        <v>0.21333333333333335</v>
       </c>
       <c r="S19" s="47">
         <f t="shared" si="27"/>
@@ -23549,7 +23563,7 @@
       </c>
       <c r="T19" s="48">
         <f t="shared" si="27"/>
-        <v>0.58666666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U19" s="11"/>
       <c r="V19" s="43" t="s">
@@ -23557,7 +23571,7 @@
       </c>
       <c r="W19" s="46">
         <f>1-W17/W18</f>
-        <v>0.75409836065573776</v>
+        <v>0.45783132530120485</v>
       </c>
       <c r="X19" s="48" t="s">
         <v>150</v>
@@ -23577,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="4">
-        <f>'Chess Clock Human-Based Grading'!C20</f>
+        <f>'Chess Clock LLM-Based Grading'!C20</f>
         <v>0</v>
       </c>
       <c r="E20" s="27"/>
@@ -23586,7 +23600,7 @@
       </c>
       <c r="G20" s="11">
         <f t="shared" ref="G20:I20" si="28">SUM(G17:G19)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="28"/>
@@ -23594,7 +23608,7 @@
       </c>
       <c r="I20" s="11">
         <f t="shared" si="28"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J20" s="11">
         <f>SUM(G17:I19)</f>
@@ -23615,7 +23629,7 @@
         <v>0.5</v>
       </c>
       <c r="D21" s="4">
-        <f>'Chess Clock Human-Based Grading'!C21</f>
+        <f>'Chess Clock LLM-Based Grading'!C21</f>
         <v>0.5</v>
       </c>
       <c r="E21" s="27"/>
@@ -23634,7 +23648,7 @@
         <v>0.5</v>
       </c>
       <c r="D22" s="4">
-        <f>'Chess Clock Human-Based Grading'!C22</f>
+        <f>'Chess Clock LLM-Based Grading'!C22</f>
         <v>0.5</v>
       </c>
       <c r="E22" s="27"/>
@@ -23659,7 +23673,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="4">
-        <f>'Chess Clock Human-Based Grading'!C23</f>
+        <f>'Chess Clock LLM-Based Grading'!C23</f>
         <v>1</v>
       </c>
       <c r="E23" s="27"/>
@@ -23729,7 +23743,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="4">
-        <f>'Chess Clock Human-Based Grading'!C24</f>
+        <f>'Chess Clock LLM-Based Grading'!C24</f>
         <v>1</v>
       </c>
       <c r="E24" s="27"/>
@@ -23778,11 +23792,11 @@
       </c>
       <c r="S24" s="41">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>6.25E-2</v>
       </c>
       <c r="T24" s="42">
         <f t="shared" si="32"/>
-        <v>0.1875</v>
+        <v>0.125</v>
       </c>
       <c r="U24" s="11"/>
       <c r="V24" s="43" t="s">
@@ -23790,7 +23804,7 @@
       </c>
       <c r="W24" s="40">
         <f>SUMPRODUCT(G24:I26, M24:O26) /$J$27</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="X24" s="42" t="s">
         <v>147</v>
@@ -23810,7 +23824,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="4">
-        <f>'Chess Clock Human-Based Grading'!C25</f>
+        <f>'Chess Clock LLM-Based Grading'!C25</f>
         <v>1</v>
       </c>
       <c r="E25" s="27"/>
@@ -23871,7 +23885,7 @@
       </c>
       <c r="W25" s="44">
         <f>SUMPRODUCT(R24:T26, M24:O26)</f>
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="X25" s="45" t="s">
         <v>149</v>
@@ -23891,7 +23905,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="4">
-        <f>'Chess Clock Human-Based Grading'!C26</f>
+        <f>'Chess Clock LLM-Based Grading'!C26</f>
         <v>1</v>
       </c>
       <c r="E26" s="27"/>
@@ -23904,11 +23918,11 @@
       </c>
       <c r="H26" s="47">
         <f>COUNTIFS($A$2:$A$90,$F$23,$C$2:$C$90,$F26,$D$2:$D$90,H$23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="48">
         <f>COUNTIFS($A$2:$A$46,$F$23,$C$2:$C$46,$F26,$D$2:$D$46,I$23) + MIN(C51,D51)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" s="11">
         <f t="shared" si="30"/>
@@ -23940,11 +23954,11 @@
       </c>
       <c r="S26" s="47">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="T26" s="48">
         <f t="shared" si="37"/>
-        <v>0.5625</v>
+        <v>0.375</v>
       </c>
       <c r="U26" s="11"/>
       <c r="V26" s="43" t="s">
@@ -23952,7 +23966,7 @@
       </c>
       <c r="W26" s="46">
         <f>1-W24/W25</f>
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="X26" s="48" t="s">
         <v>150</v>
@@ -23972,8 +23986,8 @@
         <v>0.5</v>
       </c>
       <c r="D27" s="4">
-        <f>'Chess Clock Human-Based Grading'!C27</f>
-        <v>0.5</v>
+        <f>'Chess Clock LLM-Based Grading'!C27</f>
+        <v>1</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="49" t="s">
@@ -23985,11 +23999,11 @@
       </c>
       <c r="H27" s="11">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="11">
         <f t="shared" si="38"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(G24:I26)</f>
@@ -24010,8 +24024,8 @@
         <v>1</v>
       </c>
       <c r="D28" s="4">
-        <f>'Chess Clock Human-Based Grading'!C28</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C28</f>
+        <v>0</v>
       </c>
       <c r="E28" s="27"/>
     </row>
@@ -24029,8 +24043,8 @@
         <v>1</v>
       </c>
       <c r="D29" s="4">
-        <f>'Chess Clock Human-Based Grading'!C29</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C29</f>
+        <v>0</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="67" t="s">
@@ -24054,8 +24068,8 @@
         <v>1</v>
       </c>
       <c r="D30" s="4">
-        <f>'Chess Clock Human-Based Grading'!C30</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C30</f>
+        <v>0</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="11" t="s">
@@ -24124,8 +24138,8 @@
         <v>1</v>
       </c>
       <c r="D31" s="4">
-        <f>'Chess Clock Human-Based Grading'!C31</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C31</f>
+        <v>0.5</v>
       </c>
       <c r="E31" s="27"/>
       <c r="F31" s="39">
@@ -24169,7 +24183,7 @@
       </c>
       <c r="R31" s="40">
         <f t="shared" ref="R31:T31" si="42">($J31/$J$34) * (G$34/$J$34)</f>
-        <v>4.0000000000000008E-2</v>
+        <v>0.12</v>
       </c>
       <c r="S31" s="41">
         <f t="shared" si="42"/>
@@ -24177,7 +24191,7 @@
       </c>
       <c r="T31" s="42">
         <f t="shared" si="42"/>
-        <v>0.16000000000000003</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="U31" s="11"/>
       <c r="V31" s="43" t="s">
@@ -24185,7 +24199,7 @@
       </c>
       <c r="W31" s="40">
         <f>SUMPRODUCT(G31:I33, M31:O33) /$J$34</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X31" s="42" t="s">
         <v>147</v>
@@ -24205,8 +24219,8 @@
         <v>1</v>
       </c>
       <c r="D32" s="4">
-        <f>'Chess Clock Human-Based Grading'!C32</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C32</f>
+        <v>0</v>
       </c>
       <c r="E32" s="27"/>
       <c r="F32" s="39">
@@ -24266,7 +24280,7 @@
       </c>
       <c r="W32" s="44">
         <f>SUMPRODUCT(R31:T33, M31:O33)</f>
-        <v>0.32000000000000006</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="X32" s="45" t="s">
         <v>149</v>
@@ -24286,8 +24300,8 @@
         <v>0.5</v>
       </c>
       <c r="D33" s="4">
-        <f>'Chess Clock Human-Based Grading'!C33</f>
-        <v>0.5</v>
+        <f>'Chess Clock LLM-Based Grading'!C33</f>
+        <v>1</v>
       </c>
       <c r="E33" s="27"/>
       <c r="F33" s="39">
@@ -24295,7 +24309,7 @@
       </c>
       <c r="G33" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$30,$C$2:$C$46,$F33,$D$2:$D$46,G$30) + MAX(C49-D49,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="47">
         <f>COUNTIFS($A$2:$A$90,$F$30,$C$2:$C$90,$F33,$D$2:$D$90,H$30)</f>
@@ -24303,7 +24317,7 @@
       </c>
       <c r="I33" s="48">
         <f>COUNTIFS($A$2:$A$46,$F$30,$C$2:$C$46,$F33,$D$2:$D$46,I$30) + MIN(C49,D49)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33" s="11">
         <f t="shared" si="40"/>
@@ -24331,7 +24345,7 @@
       </c>
       <c r="R33" s="46">
         <f t="shared" ref="R33:T33" si="47">($J33/$J$34) * (G$34/$J$34)</f>
-        <v>0.16000000000000003</v>
+        <v>0.48</v>
       </c>
       <c r="S33" s="47">
         <f t="shared" si="47"/>
@@ -24339,7 +24353,7 @@
       </c>
       <c r="T33" s="48">
         <f t="shared" si="47"/>
-        <v>0.64000000000000012</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="U33" s="11"/>
       <c r="V33" s="43" t="s">
@@ -24347,7 +24361,7 @@
       </c>
       <c r="W33" s="46">
         <f>1-W31/W32</f>
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="X33" s="48" t="s">
         <v>150</v>
@@ -24367,8 +24381,8 @@
         <v>1</v>
       </c>
       <c r="D34" s="4">
-        <f>'Chess Clock Human-Based Grading'!C34</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C34</f>
+        <v>0</v>
       </c>
       <c r="E34" s="27"/>
       <c r="F34" s="49" t="s">
@@ -24376,7 +24390,7 @@
       </c>
       <c r="G34" s="11">
         <f t="shared" ref="G34:I34" si="48">SUM(G31:G33)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="11">
         <f t="shared" si="48"/>
@@ -24384,7 +24398,7 @@
       </c>
       <c r="I34" s="11">
         <f t="shared" si="48"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(G31:I33)</f>
@@ -24405,8 +24419,8 @@
         <v>1</v>
       </c>
       <c r="D35" s="4">
-        <f>'Chess Clock Human-Based Grading'!C35</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C35</f>
+        <v>0</v>
       </c>
       <c r="E35" s="27"/>
     </row>
@@ -24424,8 +24438,8 @@
         <v>1</v>
       </c>
       <c r="D36" s="4">
-        <f>'Chess Clock Human-Based Grading'!C36</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C36</f>
+        <v>0</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="67" t="s">
@@ -24449,8 +24463,8 @@
         <v>1</v>
       </c>
       <c r="D37" s="4">
-        <f>'Chess Clock Human-Based Grading'!C37</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C37</f>
+        <v>0.5</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="11" t="s">
@@ -24519,8 +24533,8 @@
         <v>1</v>
       </c>
       <c r="D38" s="4">
-        <f>'Chess Clock Human-Based Grading'!C38</f>
-        <v>1</v>
+        <f>'Chess Clock LLM-Based Grading'!C38</f>
+        <v>0</v>
       </c>
       <c r="E38" s="27"/>
       <c r="F38" s="39">
@@ -24564,15 +24578,15 @@
       </c>
       <c r="R38" s="57">
         <f t="shared" ref="R38:T38" si="52">($J38/$J$41) * (G$41/$J$41)</f>
-        <v>1.2345679012345678E-2</v>
+        <v>8.6419753086419748E-2</v>
       </c>
       <c r="S38" s="58">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>2.4691358024691357E-2</v>
       </c>
       <c r="T38" s="59">
         <f t="shared" si="52"/>
-        <v>9.8765432098765427E-2</v>
+        <v>0</v>
       </c>
       <c r="U38" s="11"/>
       <c r="V38" s="43" t="s">
@@ -24580,7 +24594,7 @@
       </c>
       <c r="W38" s="40">
         <f>SUMPRODUCT(G38:I40, M38:O40) /$J$41</f>
-        <v>0</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="X38" s="42" t="s">
         <v>147</v>
@@ -24600,7 +24614,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="4">
-        <f>'Chess Clock Human-Based Grading'!C39</f>
+        <f>'Chess Clock LLM-Based Grading'!C39</f>
         <v>1</v>
       </c>
       <c r="E39" s="27"/>
@@ -24661,7 +24675,7 @@
       </c>
       <c r="W39" s="44">
         <f>SUMPRODUCT(R38:T40, M38:O40)</f>
-        <v>0.19753086419753085</v>
+        <v>0.80246913580246915</v>
       </c>
       <c r="X39" s="45" t="s">
         <v>149</v>
@@ -24681,7 +24695,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="4">
-        <f>'Chess Clock Human-Based Grading'!C40</f>
+        <f>'Chess Clock LLM-Based Grading'!C40</f>
         <v>1</v>
       </c>
       <c r="E40" s="27"/>
@@ -24690,15 +24704,15 @@
       </c>
       <c r="G40" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$37,$C$2:$C$46,$F40,$D$2:$D$46,G$37)+MAX(C50-D50,0)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H40" s="47">
         <f>COUNTIFS($A$2:$A$90,$F$37,$C$2:$C$90,$F40,$D$2:$D$90,H$37)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="48">
         <f>COUNTIFS($A$2:$A$46,$F$37,$C$2:$C$46,$F40,$D$2:$D$46,I$37) + MIN(C50,D50)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J40" s="11">
         <f t="shared" si="50"/>
@@ -24726,15 +24740,15 @@
       </c>
       <c r="R40" s="62">
         <f t="shared" ref="R40:T40" si="57">($J40/$J$41) * (G$41/$J$41)</f>
-        <v>9.8765432098765427E-2</v>
+        <v>0.69135802469135799</v>
       </c>
       <c r="S40" s="63">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>0.19753086419753085</v>
       </c>
       <c r="T40" s="64">
         <f t="shared" si="57"/>
-        <v>0.79012345679012341</v>
+        <v>0</v>
       </c>
       <c r="U40" s="11"/>
       <c r="V40" s="43" t="s">
@@ -24742,7 +24756,7 @@
       </c>
       <c r="W40" s="46">
         <f>1-W38/W39</f>
-        <v>1</v>
+        <v>3.0769230769230771E-2</v>
       </c>
       <c r="X40" s="48" t="s">
         <v>150</v>
@@ -24762,7 +24776,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="4">
-        <f>'Chess Clock Human-Based Grading'!C41</f>
+        <f>'Chess Clock LLM-Based Grading'!C41</f>
         <v>1</v>
       </c>
       <c r="E41" s="27"/>
@@ -24771,15 +24785,15 @@
       </c>
       <c r="G41" s="11">
         <f t="shared" ref="G41:I41" si="58">SUM(G38:G40)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H41" s="11">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="11">
         <f t="shared" si="58"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J41" s="11">
         <f>SUM(G38:I40)</f>
@@ -24800,7 +24814,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="4">
-        <f>'Chess Clock Human-Based Grading'!C42</f>
+        <f>'Chess Clock LLM-Based Grading'!C42</f>
         <v>1</v>
       </c>
       <c r="E42" s="27"/>
@@ -24819,7 +24833,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="4">
-        <f>'Chess Clock Human-Based Grading'!C43</f>
+        <f>'Chess Clock LLM-Based Grading'!C43</f>
         <v>1</v>
       </c>
       <c r="E43" s="27"/>
@@ -24844,7 +24858,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="4">
-        <f>'Chess Clock Human-Based Grading'!C44</f>
+        <f>'Chess Clock LLM-Based Grading'!C44</f>
         <v>1</v>
       </c>
       <c r="E44" s="27"/>
@@ -24914,7 +24928,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="4">
-        <f>'Chess Clock Human-Based Grading'!C45</f>
+        <f>'Chess Clock LLM-Based Grading'!C45</f>
         <v>1</v>
       </c>
       <c r="E45" s="27"/>
@@ -24994,8 +25008,8 @@
         <f>'Chess Clock Human-Based Grading'!C46</f>
         <v>1</v>
       </c>
-      <c r="D46" s="4">
-        <f>'Chess Clock Human-Based Grading'!C46</f>
+      <c r="D46" s="73">
+        <f>'Chess Clock LLM-Based Grading'!C46</f>
         <v>1</v>
       </c>
       <c r="E46" s="27"/>
@@ -25075,7 +25089,8 @@
         <f>'Chess Clock Human-Based Grading'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="53">
+      <c r="D47" s="4">
+        <f>'Chess Clock LLM-Based Grading'!C47</f>
         <v>0</v>
       </c>
       <c r="E47" s="27"/>
@@ -25156,6 +25171,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="4">
+        <f>'Chess Clock LLM-Based Grading'!C48</f>
         <v>0</v>
       </c>
       <c r="E48" s="27"/>
@@ -25193,6 +25209,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="4">
+        <f>'Chess Clock LLM-Based Grading'!C49</f>
         <v>0</v>
       </c>
       <c r="E49" s="27"/>
@@ -25211,6 +25228,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="4">
+        <f>'Chess Clock LLM-Based Grading'!C50</f>
         <v>0</v>
       </c>
       <c r="E50" s="27"/>
@@ -25235,6 +25253,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="4">
+        <f>'Chess Clock LLM-Based Grading'!C51</f>
         <v>0</v>
       </c>
       <c r="E51" s="27"/>
@@ -25304,6 +25323,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="4">
+        <f>'Chess Clock LLM-Based Grading'!C52</f>
         <v>0</v>
       </c>
       <c r="E52" s="27"/>
@@ -25348,15 +25368,15 @@
       </c>
       <c r="R52" s="40">
         <f t="shared" ref="R52:T52" si="72">($J52/$J$55) * (G$55/$J$55)</f>
-        <v>0.1111111111111111</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="S52" s="41">
         <f t="shared" si="72"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="T52" s="42">
         <f t="shared" si="72"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U52" s="11"/>
       <c r="V52" s="43" t="s">
@@ -25364,7 +25384,7 @@
       </c>
       <c r="W52" s="40">
         <f>SUMPRODUCT(G52:I54, M52:O54) /$J$55</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X52" s="42" t="s">
         <v>147</v>
@@ -25384,6 +25404,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="4">
+        <f>'Chess Clock LLM-Based Grading'!C53</f>
         <v>0</v>
       </c>
       <c r="E53" s="27"/>
@@ -25392,11 +25413,11 @@
       </c>
       <c r="G53" s="44">
         <f t="shared" ref="G53:I53" si="73">COUNTIFS($A$2:$A$90,$F$51,$C$2:$C$90,$F53,$D$2:$D$90,G$51)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="11">
         <f t="shared" si="73"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="45">
         <f t="shared" si="73"/>
@@ -25428,15 +25449,15 @@
       </c>
       <c r="R53" s="44">
         <f t="shared" ref="R53:T53" si="75">($J53/$J$55) * (G$55/$J$55)</f>
-        <v>0.1111111111111111</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="S53" s="11">
         <f t="shared" si="75"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="T53" s="45">
         <f t="shared" si="75"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U53" s="11"/>
       <c r="V53" s="43" t="s">
@@ -25444,7 +25465,7 @@
       </c>
       <c r="W53" s="44">
         <f>SUMPRODUCT(R52:T54, M52:O54)</f>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="X53" s="45" t="s">
         <v>149</v>
@@ -25461,7 +25482,7 @@
       </c>
       <c r="G54" s="46">
         <f>COUNTIFS($A$2:$A$46,$F$51,$C$2:$C$46,$F54,$D$2:$D$46,G$51) + MAX(C52-D52,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="47">
         <f>COUNTIFS($A$2:$A$90,$F$51,$C$2:$C$90,$F54,$D$2:$D$90,H$51)</f>
@@ -25469,7 +25490,7 @@
       </c>
       <c r="I54" s="48">
         <f>COUNTIFS($A$2:$A$46,$F$51,$C$2:$C$46,$F54,$D$2:$D$46,I$51)+MIN(C52,D52)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="11">
         <f t="shared" si="70"/>
@@ -25497,15 +25518,15 @@
       </c>
       <c r="R54" s="46">
         <f t="shared" ref="R54:T54" si="77">($J54/$J$55) * (G$55/$J$55)</f>
-        <v>0.1111111111111111</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="S54" s="47">
         <f t="shared" si="77"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="T54" s="48">
         <f t="shared" si="77"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="43" t="s">
@@ -25513,7 +25534,7 @@
       </c>
       <c r="W54" s="46">
         <f>1-W52/W53</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" s="48" t="s">
         <v>150</v>
@@ -25530,15 +25551,15 @@
       </c>
       <c r="G55" s="11">
         <f t="shared" ref="G55:I55" si="78">SUM(G52:G54)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="78"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="11">
         <f t="shared" si="78"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="11">
         <f>SUM(G52:I54)</f>
